--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>27.8</v>
+        <v>28.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>27.8</v>
+        <v>28.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>27.8</v>
+        <v>28.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>27.8</v>
+        <v>28.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.4</v>
+        <v>28.9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.5</v>
+        <v>29.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>28.8</v>
+        <v>32.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.36</v>
+        <v>3.11</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.90</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.9</v>
+        <v>30.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>31.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>28.8</v>
+        <v>32.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.35</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.90</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.9</v>
+        <v>32.4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>28.8</v>
+        <v>32.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.32</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.90</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28.1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.1</v>
+        <v>28.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>28.8</v>
+        <v>32.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.37</v>
+        <v>2.49</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.70</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.8</v>
+        <v>28.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.11</v>
+        <v>-0.35</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.90</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>-0.33</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.90</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>-0.31</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.90</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.49</v>
+        <v>-0.36</v>
       </c>
       <c r="H5" t="n">
         <v>0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.70</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
         <v>34.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
         <v>34.1</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.33</v>
+        <v>0.66</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
         <v>34.1</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.31</v>
+        <v>0.62</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
         <v>34.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.36</v>
+        <v>0.36</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.9</v>
+        <v>30.7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.1</v>
+        <v>30.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.4</v>
+        <v>32.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.6</v>
+        <v>34.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.7</v>
+        <v>32.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>32.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>34.6</v>
+        <v>38.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.2</v>
+        <v>33.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.2</v>
+        <v>34.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>34.6</v>
+        <v>38.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.2</v>
+        <v>35.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>34.6</v>
+        <v>38.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.5</v>
+        <v>31</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.4</v>
+        <v>31.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>34.6</v>
+        <v>38.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.34</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.60</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>38.3</v>
+        <v>39.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>-0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34.4</v>
+        <v>33.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>38.3</v>
+        <v>39.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.47</v>
+        <v>-0.59</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.4</v>
+        <v>35.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>38.3</v>
+        <v>39.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>38.3</v>
+        <v>39.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>-0.65</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.60</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.65</v>
+        <v>0.32</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F2" t="n">
-        <v>38.5</v>
+        <v>34.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31</v>
+        <v>-2.47</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>38.5</v>
+        <v>34.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>-2.36</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F4" t="n">
-        <v>38.5</v>
+        <v>34.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.28</v>
+        <v>-2.23</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.1</v>
+        <v>30.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>38.5</v>
+        <v>34.3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>-2.58</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>34.3</v>
+        <v>36.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.47</v>
+        <v>0.31</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>34.3</v>
+        <v>36.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.36</v>
+        <v>0.29</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>34.3</v>
+        <v>36.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.23</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.2</v>
+        <v>31.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>34.3</v>
+        <v>36.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.58</v>
+        <v>0.32</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31</v>
+        <v>-1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>-1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.28</v>
+        <v>-1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.1</v>
+        <v>30.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>-1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>37.3</v>
+        <v>34.7</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.54</v>
+        <v>0.31</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.4</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>37.3</v>
+        <v>34.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.47</v>
+        <v>0.29</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>37.3</v>
+        <v>34.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.39</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.5</v>
+        <v>31.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>37.3</v>
+        <v>34.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.61</v>
+        <v>0.32</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>34.7</v>
+        <v>36.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>34.7</v>
+        <v>36.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>34.7</v>
+        <v>36.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>34.7</v>
+        <v>36.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>36.9</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>36.9</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>36.9</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>36.9</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.23</v>
+        <v>1.23</v>
       </c>
       <c r="H2" t="n">
         <v>-0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.18</v>
+        <v>1.18</v>
       </c>
       <c r="H3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I3" t="n">
         <v>-0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.5</v>
+        <v>36.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.11</v>
+        <v>1.11</v>
       </c>
       <c r="H4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.29</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>1.23</v>
+        <v>-0.62</v>
       </c>
       <c r="H2" t="n">
         <v>-0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.18</v>
+        <v>-0.59</v>
       </c>
       <c r="H3" t="n">
         <v>-0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.3</v>
+        <v>35.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>-0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>-0.65</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>30.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>30.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.59</v>
+        <v>-0.29</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>30.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>30.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.4</v>
+        <v>31.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.31</v>
+        <v>1.59</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.9</v>
+        <v>32.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.29</v>
+        <v>1.52</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.28</v>
+        <v>1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>30.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.32</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.4</v>
+        <v>30.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>28.8</v>
+        <v>27.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.59</v>
+        <v>0.33</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.9</v>
+        <v>31.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>28.8</v>
+        <v>27.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>28.8</v>
+        <v>27.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1.43</v>
+        <v>0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.3</v>
+        <v>29.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>29.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>28.8</v>
+        <v>27.9</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.4</v>
+        <v>29.8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.33</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.9</v>
+        <v>31.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.31</v>
+        <v>0.96</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.29</v>
+        <v>0.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.7</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F2" t="n">
         <v>30.1</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.5</v>
-      </c>
       <c r="G2" t="n">
-        <v>1.01</v>
+        <v>-1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.96</v>
+        <v>-0.96</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9</v>
+        <v>-0.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F2" t="n">
-        <v>31.3</v>
+        <v>32.4</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.60</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F3" t="n">
-        <v>31.3</v>
+        <v>32.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.60</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.3</v>
+        <v>34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>31.3</v>
+        <v>32.4</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.60</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>28.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>31.3</v>
+        <v>32.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.97</v>
+        <v>0.66</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.60</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.88</v>
+        <v>0.63</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.60</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.76</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.60</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.71</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.66</v>
+        <v>-0.33</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.63</v>
+        <v>-0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.59</v>
+        <v>-0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.33</v>
+        <v>-0.66</v>
       </c>
       <c r="H2" t="n">
         <v>-0.02</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.31</v>
+        <v>-0.62</v>
       </c>
       <c r="H3" t="n">
         <v>-0.02</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.29</v>
+        <v>-0.59</v>
       </c>
       <c r="H4" t="n">
         <v>-0.02</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.34</v>
+        <v>-0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>-0.01</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>32.8</v>
+        <v>35.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.66</v>
+        <v>-0.98</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -541,29 +541,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>32.8</v>
+        <v>35.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.62</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -582,29 +582,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>32.8</v>
+        <v>35.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.59</v>
+        <v>-0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -623,29 +623,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>32.8</v>
+        <v>35.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.68</v>
+        <v>-1.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
